--- a/data/card_rates.xlsx
+++ b/data/card_rates.xlsx
@@ -669,6 +669,11 @@
         <v>0</v>
       </c>
       <c r="W2" s="8" t="n"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>assets/cards/uob_one_card.png</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -742,6 +747,11 @@
         <v>0</v>
       </c>
       <c r="W3" s="8" t="n"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>assets/cards/uob_one_card.png</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -815,6 +825,11 @@
         <v>0</v>
       </c>
       <c r="W4" s="8" t="n"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>assets/cards/uob_one_card.png</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -888,6 +903,11 @@
         <v>0</v>
       </c>
       <c r="W5" s="8" t="n"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>assets/cards/uob_evol_card.png</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -961,6 +981,11 @@
         <v>0</v>
       </c>
       <c r="W6" s="8" t="n"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>assets/cards/uob_absolute_cashback_card.png</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1034,6 +1059,11 @@
         <v>27</v>
       </c>
       <c r="W7" s="9" t="n"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>assets/cards/uob_preferred_visa_card.png</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1107,6 +1137,11 @@
         <v>27</v>
       </c>
       <c r="W8" s="9" t="n"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>assets/cards/uob_visa_signature_card.png</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1180,6 +1215,11 @@
         <v>27</v>
       </c>
       <c r="W9" s="9" t="n"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>assets/cards/uob_prvi_miles_card.png</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1253,6 +1293,11 @@
         <v>27</v>
       </c>
       <c r="W10" s="9" t="n"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>assets/cards/uob_ladys_card.png</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1326,6 +1371,11 @@
         <v>0</v>
       </c>
       <c r="W11" s="9" t="n"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>assets/cards/uob_visa_infinite_metal_card.png</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
